--- a/SuppXLS/Scen_RES_SHARE_90%_24_7_LO.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_90%_24_7_LO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yukiainge/Documents/Claude/Projects/Energy Modeling &amp; Climate Policy/05_TIMES_Modeling/models/Models MSc_SELECT_updated-20260612/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67D8BCF1-4FE8-BC43-8051-0A996671B5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEAE3A3-39DE-8B47-BABC-D36899F4AE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,10 +68,10 @@
     <t>FLO_SHAR</t>
   </si>
   <si>
-    <t>ANNUAL</t>
+    <t>LO</t>
   </si>
   <si>
-    <t>LO</t>
+    <t>DAYNITE</t>
   </si>
 </sst>
 </file>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
@@ -4463,7 +4463,7 @@
         <v>2030</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" s="5">
         <v>0.9</v>

--- a/SuppXLS/Scen_RES_SHARE_90%_24_7_LO.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_90%_24_7_LO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yukiainge/Documents/Claude/Projects/Energy Modeling &amp; Climate Policy/05_TIMES_Modeling/models/Models MSc_SELECT_updated-20260612/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEAE3A3-39DE-8B47-BABC-D36899F4AE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EC8AD7-05D7-8D41-9909-59AB8DD960C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Year</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>2023,2025, 2030, 2035, 2040, 2045, 2050</t>
   </si>
 </sst>
 </file>
@@ -4459,8 +4462,8 @@
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2">
-        <v>2030</v>
+      <c r="F5" t="s">
+        <v>13</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>11</v>

--- a/SuppXLS/Scen_RES_SHARE_90%_24_7_LO.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_90%_24_7_LO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yukiainge/Documents/Claude/Projects/Energy Modeling &amp; Climate Policy/05_TIMES_Modeling/models/Models MSc_SELECT_updated-20260612/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EC8AD7-05D7-8D41-9909-59AB8DD960C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A1ED66-07C0-ED4D-B3F1-3BD33E58A026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="8920" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INS_1" sheetId="11" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="13">
   <si>
     <t>Year</t>
   </si>
@@ -73,9 +73,6 @@
   <si>
     <t>DAYNITE</t>
   </si>
-  <si>
-    <t>2023,2025, 2030, 2035, 2040, 2045, 2050</t>
-  </si>
 </sst>
 </file>
 
@@ -102,7 +99,7 @@
     <numFmt numFmtId="179" formatCode="yyyy"/>
     <numFmt numFmtId="180" formatCode="_-* ###0.00_-;\(###0.00\);_-* &quot;–&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="106">
+  <fonts count="107">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -792,6 +789,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1023,7 +1027,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1262,6 +1266,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2813,7 +2828,7 @@
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="104" fillId="41" borderId="18" xfId="1280" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2826,6 +2841,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1279" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1281">
     <cellStyle name="20 % - Akzent1 2" xfId="338" xr:uid="{F45CA455-86B7-48DC-AA00-C66E9CC6D9BA}"/>
@@ -4410,7 +4432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:H5"/>
+  <dimension ref="B3:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -4449,7 +4471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" ht="16" thickBot="1">
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
@@ -4462,13 +4484,128 @@
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
-        <v>13</v>
+      <c r="F5">
+        <v>2025</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="16" thickBot="1">
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2030</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="16" thickBot="1">
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="8">
+        <v>2035</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="16" thickBot="1">
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="8">
+        <v>2040</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="16" thickBot="1">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2045</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="10">
+        <v>2050</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="5">
         <v>0.9</v>
       </c>
     </row>
